--- a/dashboard/autogen/CN308_313.xlsx
+++ b/dashboard/autogen/CN308_313.xlsx
@@ -458,7 +458,7 @@
           <t>SELECT ma_benh,
        ten_benh,
        ten_nhom,
-       COUNT(DISTINCT ma_bn) AS so_ca,
+       COUNT(DISTINCT ma_bn, cccd) AS so_ca,
        SUM(so_luot)          AS so_luot,
        SUM(so_tu_vong)       AS so_tu_vong
 FROM emr_db_tong_hop_benh_nhom
@@ -511,7 +511,7 @@
           <t>SELECT ma_benh,
        ten_benh,
        ten_chuong,
-       COUNT(DISTINCT ma_bn) AS so_ca,
+       COUNT(DISTINCT ma_bn, cccd) AS so_ca,
        SUM(so_luot)          AS so_luot,
        SUM(so_tu_vong)       AS so_tu_vong
 FROM emr_db_tong_hop_benh_chuong
@@ -560,7 +560,7 @@
       <c r="F4" s="9" t="inlineStr">
         <is>
           <t>SELECT ten_nhom,
-       COUNT(DISTINCT ma_bn) AS so_ca
+       COUNT(DISTINCT ma_bn, cccd) AS so_ca
 FROM emr_db_tong_hop_benh_nhom
 WHERE ma_csyt = :ma_csyt
   AND ngay_ghi_nhan &gt;= :from_date
